--- a/InputData/indst/IFTQfS/Indst Fuels Qualifying for Support.xlsx
+++ b/InputData/indst/IFTQfS/Indst Fuels Qualifying for Support.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IFTQfS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\IFTQfS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6495CBB6-BB3C-4AAF-9DDF-221DA0A91E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5762D799-CFFF-4A7C-B40C-142544465721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26910" yWindow="1440" windowWidth="25980" windowHeight="14640" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
   <si>
     <t>Source:</t>
   </si>
@@ -100,12 +100,6 @@
   </si>
   <si>
     <t xml:space="preserve">and low-interest government loans to reduce the cost of financing clean equipment. </t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
   <si>
     <t>IFTQfS Industrial Fuel Types Qualifying for Clean Heat Production Subsidy</t>
@@ -506,12 +500,12 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -534,12 +528,12 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -580,7 +574,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
@@ -672,22 +666,6 @@
       </c>
       <c r="B11">
         <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +678,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
@@ -792,22 +770,6 @@
       </c>
       <c r="B11">
         <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -820,7 +782,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
@@ -914,22 +876,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
